--- a/EndResult/100m Butterfly.xlsx
+++ b/EndResult/100m Butterfly.xlsx
@@ -1549,7 +1549,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>03.12.2016</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Amanda Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>03.12.2016</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">

--- a/EndResult/100m Butterfly.xlsx
+++ b/EndResult/100m Butterfly.xlsx
@@ -1514,25 +1514,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tove Fludal Haugan</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.07,61</t>
+          <t>1.07,47</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>03.03.2005</t>
+          <t>30.05.2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1549,25 +1549,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Tove Fludal Haugan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.08,12</t>
+          <t>1.07,61</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>03.12.2016</t>
+          <t>03.03.2005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>03.12.2016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1705,25 +1705,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sara Alonso Lopez</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.06,61</t>
+          <t>1.05,52</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.01.2023</t>
+          <t>21.03.2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1740,25 +1740,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alma van der Hagen</t>
+          <t>Sara Alonso Lopez</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.07,80</t>
+          <t>1.06,61</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05.04.2025</t>
+          <t>27.01.2023</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1775,25 +1775,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vilde Holan Bye</t>
+          <t>Alma van der Hagen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.08,19</t>
+          <t>1.07,80</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28.02.2015</t>
+          <t>05.04.2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1810,25 +1810,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Vilde Holan Bye</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.08,36</t>
+          <t>1.08,19</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.07.2017</t>
+          <t>28.02.2015</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1845,25 +1845,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eirill Straum</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.08,77</t>
+          <t>1.08,36</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.07.2018</t>
+          <t>10.07.2017</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tøyen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1880,25 +1880,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tove Fludal Haugan</t>
+          <t>Eirill Straum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.08,98</t>
+          <t>1.08,77</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09.07.2005</t>
+          <t>14.07.2018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1915,25 +1915,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Monica Martinsen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.09,42</t>
+          <t>1.08,87</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.07.2008</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1950,25 +1950,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Henriette Martinsen</t>
+          <t>Tove Fludal Haugan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.09,56</t>
+          <t>1.08,98</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25.04.2009</t>
+          <t>09.07.2005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1985,25 +1985,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Monica Martinsen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.09,94</t>
+          <t>1.09,42</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31.05.2015</t>
+          <t>12.07.2008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
